--- a/temp/MACRO_VISA_20250516.xlsx
+++ b/temp/MACRO_VISA_20250516.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-1952341.38</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-1952341,38</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2526.56</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2526,56</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
